--- a/tracker/templates/TEMPLATE_OpenQuestions.xlsx
+++ b/tracker/templates/TEMPLATE_OpenQuestions.xlsx
@@ -9,7 +9,9 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open Questions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'Open Questions'!$7:$7</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -17,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -27,14 +29,18 @@
     </font>
     <font>
       <b val="1"/>
-      <sz val="13"/>
+      <color rgb="001F4E78"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -43,11 +49,16 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00DDEBF7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="001F4E78"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -55,28 +66,55 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="2">
     <dxf>
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="00FFF2CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00F2F2F2"/>
         </patternFill>
       </fill>
     </dxf>
@@ -440,557 +478,590 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C103"/>
+  <dimension ref="A1:C107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="11" customWidth="1" min="1" max="1"/>
-    <col width="100" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="90" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Job ________ - ________________</t>
+          <t>OPEN QUESTIONS</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2">
-        <f>COUNTIF(A4:A103,"Open")&amp;" open - ready to ship when this is 0 and every unit and filter is accounted for"</f>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Job number</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n"/>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Project name</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n"/>
+    </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Airco PM</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n"/>
+    </row>
+    <row r="5">
+      <c r="B5" s="4">
+        <f>COUNTIF(A8:A107,"Open")&amp;" open - ready to send when this is 0 and every unit and filter is accounted for"</f>
         <v/>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+    <row r="7" ht="34" customHeight="1">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>Question</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>Who knows</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="3" t="n"/>
-      <c r="B4" s="3" t="n"/>
-      <c r="C4" s="3" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="n"/>
-      <c r="B5" s="3" t="n"/>
-      <c r="C5" s="3" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="n"/>
-      <c r="B6" s="3" t="n"/>
-      <c r="C6" s="3" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="n"/>
-      <c r="B7" s="3" t="n"/>
-      <c r="C7" s="3" t="n"/>
-    </row>
     <row r="8">
-      <c r="A8" s="3" t="n"/>
-      <c r="B8" s="3" t="n"/>
-      <c r="C8" s="3" t="n"/>
+      <c r="A8" s="6" t="n"/>
+      <c r="B8" s="7" t="n"/>
+      <c r="C8" s="7" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="n"/>
-      <c r="B9" s="3" t="n"/>
-      <c r="C9" s="3" t="n"/>
+      <c r="A9" s="6" t="n"/>
+      <c r="B9" s="7" t="n"/>
+      <c r="C9" s="7" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="n"/>
-      <c r="B10" s="3" t="n"/>
-      <c r="C10" s="3" t="n"/>
+      <c r="A10" s="6" t="n"/>
+      <c r="B10" s="7" t="n"/>
+      <c r="C10" s="7" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="n"/>
-      <c r="B11" s="3" t="n"/>
-      <c r="C11" s="3" t="n"/>
+      <c r="A11" s="6" t="n"/>
+      <c r="B11" s="7" t="n"/>
+      <c r="C11" s="7" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="n"/>
-      <c r="B12" s="3" t="n"/>
-      <c r="C12" s="3" t="n"/>
+      <c r="A12" s="6" t="n"/>
+      <c r="B12" s="7" t="n"/>
+      <c r="C12" s="7" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="n"/>
-      <c r="B13" s="3" t="n"/>
-      <c r="C13" s="3" t="n"/>
+      <c r="A13" s="6" t="n"/>
+      <c r="B13" s="7" t="n"/>
+      <c r="C13" s="7" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="n"/>
-      <c r="B14" s="3" t="n"/>
-      <c r="C14" s="3" t="n"/>
+      <c r="A14" s="6" t="n"/>
+      <c r="B14" s="7" t="n"/>
+      <c r="C14" s="7" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="n"/>
-      <c r="B15" s="3" t="n"/>
-      <c r="C15" s="3" t="n"/>
+      <c r="A15" s="6" t="n"/>
+      <c r="B15" s="7" t="n"/>
+      <c r="C15" s="7" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="n"/>
-      <c r="B16" s="3" t="n"/>
-      <c r="C16" s="3" t="n"/>
+      <c r="A16" s="6" t="n"/>
+      <c r="B16" s="7" t="n"/>
+      <c r="C16" s="7" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="n"/>
-      <c r="B17" s="3" t="n"/>
-      <c r="C17" s="3" t="n"/>
+      <c r="A17" s="6" t="n"/>
+      <c r="B17" s="7" t="n"/>
+      <c r="C17" s="7" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="n"/>
-      <c r="B18" s="3" t="n"/>
-      <c r="C18" s="3" t="n"/>
+      <c r="A18" s="6" t="n"/>
+      <c r="B18" s="7" t="n"/>
+      <c r="C18" s="7" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="n"/>
-      <c r="B19" s="3" t="n"/>
-      <c r="C19" s="3" t="n"/>
+      <c r="A19" s="6" t="n"/>
+      <c r="B19" s="7" t="n"/>
+      <c r="C19" s="7" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="n"/>
-      <c r="B20" s="3" t="n"/>
-      <c r="C20" s="3" t="n"/>
+      <c r="A20" s="6" t="n"/>
+      <c r="B20" s="7" t="n"/>
+      <c r="C20" s="7" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="n"/>
-      <c r="B21" s="3" t="n"/>
-      <c r="C21" s="3" t="n"/>
+      <c r="A21" s="6" t="n"/>
+      <c r="B21" s="7" t="n"/>
+      <c r="C21" s="7" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="n"/>
-      <c r="B22" s="3" t="n"/>
-      <c r="C22" s="3" t="n"/>
+      <c r="A22" s="6" t="n"/>
+      <c r="B22" s="7" t="n"/>
+      <c r="C22" s="7" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="n"/>
-      <c r="B23" s="3" t="n"/>
-      <c r="C23" s="3" t="n"/>
+      <c r="A23" s="6" t="n"/>
+      <c r="B23" s="7" t="n"/>
+      <c r="C23" s="7" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="n"/>
-      <c r="B24" s="3" t="n"/>
-      <c r="C24" s="3" t="n"/>
+      <c r="A24" s="6" t="n"/>
+      <c r="B24" s="7" t="n"/>
+      <c r="C24" s="7" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="n"/>
-      <c r="B25" s="3" t="n"/>
-      <c r="C25" s="3" t="n"/>
+      <c r="A25" s="6" t="n"/>
+      <c r="B25" s="7" t="n"/>
+      <c r="C25" s="7" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="n"/>
-      <c r="B26" s="3" t="n"/>
-      <c r="C26" s="3" t="n"/>
+      <c r="A26" s="6" t="n"/>
+      <c r="B26" s="7" t="n"/>
+      <c r="C26" s="7" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="n"/>
-      <c r="B27" s="3" t="n"/>
-      <c r="C27" s="3" t="n"/>
+      <c r="A27" s="6" t="n"/>
+      <c r="B27" s="7" t="n"/>
+      <c r="C27" s="7" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="n"/>
-      <c r="B28" s="3" t="n"/>
-      <c r="C28" s="3" t="n"/>
+      <c r="A28" s="6" t="n"/>
+      <c r="B28" s="7" t="n"/>
+      <c r="C28" s="7" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="n"/>
-      <c r="B29" s="3" t="n"/>
-      <c r="C29" s="3" t="n"/>
+      <c r="A29" s="6" t="n"/>
+      <c r="B29" s="7" t="n"/>
+      <c r="C29" s="7" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="n"/>
-      <c r="B30" s="3" t="n"/>
-      <c r="C30" s="3" t="n"/>
+      <c r="A30" s="6" t="n"/>
+      <c r="B30" s="7" t="n"/>
+      <c r="C30" s="7" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="n"/>
-      <c r="B31" s="3" t="n"/>
-      <c r="C31" s="3" t="n"/>
+      <c r="A31" s="6" t="n"/>
+      <c r="B31" s="7" t="n"/>
+      <c r="C31" s="7" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="n"/>
-      <c r="B32" s="3" t="n"/>
-      <c r="C32" s="3" t="n"/>
+      <c r="A32" s="6" t="n"/>
+      <c r="B32" s="7" t="n"/>
+      <c r="C32" s="7" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="3" t="n"/>
-      <c r="B33" s="3" t="n"/>
-      <c r="C33" s="3" t="n"/>
+      <c r="A33" s="6" t="n"/>
+      <c r="B33" s="7" t="n"/>
+      <c r="C33" s="7" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="3" t="n"/>
-      <c r="B34" s="3" t="n"/>
-      <c r="C34" s="3" t="n"/>
+      <c r="A34" s="6" t="n"/>
+      <c r="B34" s="7" t="n"/>
+      <c r="C34" s="7" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="3" t="n"/>
-      <c r="B35" s="3" t="n"/>
-      <c r="C35" s="3" t="n"/>
+      <c r="A35" s="6" t="n"/>
+      <c r="B35" s="7" t="n"/>
+      <c r="C35" s="7" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="3" t="n"/>
-      <c r="B36" s="3" t="n"/>
-      <c r="C36" s="3" t="n"/>
+      <c r="A36" s="6" t="n"/>
+      <c r="B36" s="7" t="n"/>
+      <c r="C36" s="7" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="3" t="n"/>
-      <c r="B37" s="3" t="n"/>
-      <c r="C37" s="3" t="n"/>
+      <c r="A37" s="6" t="n"/>
+      <c r="B37" s="7" t="n"/>
+      <c r="C37" s="7" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="3" t="n"/>
-      <c r="B38" s="3" t="n"/>
-      <c r="C38" s="3" t="n"/>
+      <c r="A38" s="6" t="n"/>
+      <c r="B38" s="7" t="n"/>
+      <c r="C38" s="7" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="3" t="n"/>
-      <c r="B39" s="3" t="n"/>
-      <c r="C39" s="3" t="n"/>
+      <c r="A39" s="6" t="n"/>
+      <c r="B39" s="7" t="n"/>
+      <c r="C39" s="7" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="3" t="n"/>
-      <c r="B40" s="3" t="n"/>
-      <c r="C40" s="3" t="n"/>
+      <c r="A40" s="6" t="n"/>
+      <c r="B40" s="7" t="n"/>
+      <c r="C40" s="7" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="3" t="n"/>
-      <c r="B41" s="3" t="n"/>
-      <c r="C41" s="3" t="n"/>
+      <c r="A41" s="6" t="n"/>
+      <c r="B41" s="7" t="n"/>
+      <c r="C41" s="7" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="3" t="n"/>
-      <c r="B42" s="3" t="n"/>
-      <c r="C42" s="3" t="n"/>
+      <c r="A42" s="6" t="n"/>
+      <c r="B42" s="7" t="n"/>
+      <c r="C42" s="7" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="3" t="n"/>
-      <c r="B43" s="3" t="n"/>
-      <c r="C43" s="3" t="n"/>
+      <c r="A43" s="6" t="n"/>
+      <c r="B43" s="7" t="n"/>
+      <c r="C43" s="7" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="3" t="n"/>
-      <c r="B44" s="3" t="n"/>
-      <c r="C44" s="3" t="n"/>
+      <c r="A44" s="6" t="n"/>
+      <c r="B44" s="7" t="n"/>
+      <c r="C44" s="7" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="3" t="n"/>
-      <c r="B45" s="3" t="n"/>
-      <c r="C45" s="3" t="n"/>
+      <c r="A45" s="6" t="n"/>
+      <c r="B45" s="7" t="n"/>
+      <c r="C45" s="7" t="n"/>
     </row>
     <row r="46">
-      <c r="A46" s="3" t="n"/>
-      <c r="B46" s="3" t="n"/>
-      <c r="C46" s="3" t="n"/>
+      <c r="A46" s="6" t="n"/>
+      <c r="B46" s="7" t="n"/>
+      <c r="C46" s="7" t="n"/>
     </row>
     <row r="47">
-      <c r="A47" s="3" t="n"/>
-      <c r="B47" s="3" t="n"/>
-      <c r="C47" s="3" t="n"/>
+      <c r="A47" s="6" t="n"/>
+      <c r="B47" s="7" t="n"/>
+      <c r="C47" s="7" t="n"/>
     </row>
     <row r="48">
-      <c r="A48" s="3" t="n"/>
-      <c r="B48" s="3" t="n"/>
-      <c r="C48" s="3" t="n"/>
+      <c r="A48" s="6" t="n"/>
+      <c r="B48" s="7" t="n"/>
+      <c r="C48" s="7" t="n"/>
     </row>
     <row r="49">
-      <c r="A49" s="3" t="n"/>
-      <c r="B49" s="3" t="n"/>
-      <c r="C49" s="3" t="n"/>
+      <c r="A49" s="6" t="n"/>
+      <c r="B49" s="7" t="n"/>
+      <c r="C49" s="7" t="n"/>
     </row>
     <row r="50">
-      <c r="A50" s="3" t="n"/>
-      <c r="B50" s="3" t="n"/>
-      <c r="C50" s="3" t="n"/>
+      <c r="A50" s="6" t="n"/>
+      <c r="B50" s="7" t="n"/>
+      <c r="C50" s="7" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="3" t="n"/>
-      <c r="B51" s="3" t="n"/>
-      <c r="C51" s="3" t="n"/>
+      <c r="A51" s="6" t="n"/>
+      <c r="B51" s="7" t="n"/>
+      <c r="C51" s="7" t="n"/>
     </row>
     <row r="52">
-      <c r="A52" s="3" t="n"/>
-      <c r="B52" s="3" t="n"/>
-      <c r="C52" s="3" t="n"/>
+      <c r="A52" s="6" t="n"/>
+      <c r="B52" s="7" t="n"/>
+      <c r="C52" s="7" t="n"/>
     </row>
     <row r="53">
-      <c r="A53" s="3" t="n"/>
-      <c r="B53" s="3" t="n"/>
-      <c r="C53" s="3" t="n"/>
+      <c r="A53" s="6" t="n"/>
+      <c r="B53" s="7" t="n"/>
+      <c r="C53" s="7" t="n"/>
     </row>
     <row r="54">
-      <c r="A54" s="3" t="n"/>
-      <c r="B54" s="3" t="n"/>
-      <c r="C54" s="3" t="n"/>
+      <c r="A54" s="6" t="n"/>
+      <c r="B54" s="7" t="n"/>
+      <c r="C54" s="7" t="n"/>
     </row>
     <row r="55">
-      <c r="A55" s="3" t="n"/>
-      <c r="B55" s="3" t="n"/>
-      <c r="C55" s="3" t="n"/>
+      <c r="A55" s="6" t="n"/>
+      <c r="B55" s="7" t="n"/>
+      <c r="C55" s="7" t="n"/>
     </row>
     <row r="56">
-      <c r="A56" s="3" t="n"/>
-      <c r="B56" s="3" t="n"/>
-      <c r="C56" s="3" t="n"/>
+      <c r="A56" s="6" t="n"/>
+      <c r="B56" s="7" t="n"/>
+      <c r="C56" s="7" t="n"/>
     </row>
     <row r="57">
-      <c r="A57" s="3" t="n"/>
-      <c r="B57" s="3" t="n"/>
-      <c r="C57" s="3" t="n"/>
+      <c r="A57" s="6" t="n"/>
+      <c r="B57" s="7" t="n"/>
+      <c r="C57" s="7" t="n"/>
     </row>
     <row r="58">
-      <c r="A58" s="3" t="n"/>
-      <c r="B58" s="3" t="n"/>
-      <c r="C58" s="3" t="n"/>
+      <c r="A58" s="6" t="n"/>
+      <c r="B58" s="7" t="n"/>
+      <c r="C58" s="7" t="n"/>
     </row>
     <row r="59">
-      <c r="A59" s="3" t="n"/>
-      <c r="B59" s="3" t="n"/>
-      <c r="C59" s="3" t="n"/>
+      <c r="A59" s="6" t="n"/>
+      <c r="B59" s="7" t="n"/>
+      <c r="C59" s="7" t="n"/>
     </row>
     <row r="60">
-      <c r="A60" s="3" t="n"/>
-      <c r="B60" s="3" t="n"/>
-      <c r="C60" s="3" t="n"/>
+      <c r="A60" s="6" t="n"/>
+      <c r="B60" s="7" t="n"/>
+      <c r="C60" s="7" t="n"/>
     </row>
     <row r="61">
-      <c r="A61" s="3" t="n"/>
-      <c r="B61" s="3" t="n"/>
-      <c r="C61" s="3" t="n"/>
+      <c r="A61" s="6" t="n"/>
+      <c r="B61" s="7" t="n"/>
+      <c r="C61" s="7" t="n"/>
     </row>
     <row r="62">
-      <c r="A62" s="3" t="n"/>
-      <c r="B62" s="3" t="n"/>
-      <c r="C62" s="3" t="n"/>
+      <c r="A62" s="6" t="n"/>
+      <c r="B62" s="7" t="n"/>
+      <c r="C62" s="7" t="n"/>
     </row>
     <row r="63">
-      <c r="A63" s="3" t="n"/>
-      <c r="B63" s="3" t="n"/>
-      <c r="C63" s="3" t="n"/>
+      <c r="A63" s="6" t="n"/>
+      <c r="B63" s="7" t="n"/>
+      <c r="C63" s="7" t="n"/>
     </row>
     <row r="64">
-      <c r="A64" s="3" t="n"/>
-      <c r="B64" s="3" t="n"/>
-      <c r="C64" s="3" t="n"/>
+      <c r="A64" s="6" t="n"/>
+      <c r="B64" s="7" t="n"/>
+      <c r="C64" s="7" t="n"/>
     </row>
     <row r="65">
-      <c r="A65" s="3" t="n"/>
-      <c r="B65" s="3" t="n"/>
-      <c r="C65" s="3" t="n"/>
+      <c r="A65" s="6" t="n"/>
+      <c r="B65" s="7" t="n"/>
+      <c r="C65" s="7" t="n"/>
     </row>
     <row r="66">
-      <c r="A66" s="3" t="n"/>
-      <c r="B66" s="3" t="n"/>
-      <c r="C66" s="3" t="n"/>
+      <c r="A66" s="6" t="n"/>
+      <c r="B66" s="7" t="n"/>
+      <c r="C66" s="7" t="n"/>
     </row>
     <row r="67">
-      <c r="A67" s="3" t="n"/>
-      <c r="B67" s="3" t="n"/>
-      <c r="C67" s="3" t="n"/>
+      <c r="A67" s="6" t="n"/>
+      <c r="B67" s="7" t="n"/>
+      <c r="C67" s="7" t="n"/>
     </row>
     <row r="68">
-      <c r="A68" s="3" t="n"/>
-      <c r="B68" s="3" t="n"/>
-      <c r="C68" s="3" t="n"/>
+      <c r="A68" s="6" t="n"/>
+      <c r="B68" s="7" t="n"/>
+      <c r="C68" s="7" t="n"/>
     </row>
     <row r="69">
-      <c r="A69" s="3" t="n"/>
-      <c r="B69" s="3" t="n"/>
-      <c r="C69" s="3" t="n"/>
+      <c r="A69" s="6" t="n"/>
+      <c r="B69" s="7" t="n"/>
+      <c r="C69" s="7" t="n"/>
     </row>
     <row r="70">
-      <c r="A70" s="3" t="n"/>
-      <c r="B70" s="3" t="n"/>
-      <c r="C70" s="3" t="n"/>
+      <c r="A70" s="6" t="n"/>
+      <c r="B70" s="7" t="n"/>
+      <c r="C70" s="7" t="n"/>
     </row>
     <row r="71">
-      <c r="A71" s="3" t="n"/>
-      <c r="B71" s="3" t="n"/>
-      <c r="C71" s="3" t="n"/>
+      <c r="A71" s="6" t="n"/>
+      <c r="B71" s="7" t="n"/>
+      <c r="C71" s="7" t="n"/>
     </row>
     <row r="72">
-      <c r="A72" s="3" t="n"/>
-      <c r="B72" s="3" t="n"/>
-      <c r="C72" s="3" t="n"/>
+      <c r="A72" s="6" t="n"/>
+      <c r="B72" s="7" t="n"/>
+      <c r="C72" s="7" t="n"/>
     </row>
     <row r="73">
-      <c r="A73" s="3" t="n"/>
-      <c r="B73" s="3" t="n"/>
-      <c r="C73" s="3" t="n"/>
+      <c r="A73" s="6" t="n"/>
+      <c r="B73" s="7" t="n"/>
+      <c r="C73" s="7" t="n"/>
     </row>
     <row r="74">
-      <c r="A74" s="3" t="n"/>
-      <c r="B74" s="3" t="n"/>
-      <c r="C74" s="3" t="n"/>
+      <c r="A74" s="6" t="n"/>
+      <c r="B74" s="7" t="n"/>
+      <c r="C74" s="7" t="n"/>
     </row>
     <row r="75">
-      <c r="A75" s="3" t="n"/>
-      <c r="B75" s="3" t="n"/>
-      <c r="C75" s="3" t="n"/>
+      <c r="A75" s="6" t="n"/>
+      <c r="B75" s="7" t="n"/>
+      <c r="C75" s="7" t="n"/>
     </row>
     <row r="76">
-      <c r="A76" s="3" t="n"/>
-      <c r="B76" s="3" t="n"/>
-      <c r="C76" s="3" t="n"/>
+      <c r="A76" s="6" t="n"/>
+      <c r="B76" s="7" t="n"/>
+      <c r="C76" s="7" t="n"/>
     </row>
     <row r="77">
-      <c r="A77" s="3" t="n"/>
-      <c r="B77" s="3" t="n"/>
-      <c r="C77" s="3" t="n"/>
+      <c r="A77" s="6" t="n"/>
+      <c r="B77" s="7" t="n"/>
+      <c r="C77" s="7" t="n"/>
     </row>
     <row r="78">
-      <c r="A78" s="3" t="n"/>
-      <c r="B78" s="3" t="n"/>
-      <c r="C78" s="3" t="n"/>
+      <c r="A78" s="6" t="n"/>
+      <c r="B78" s="7" t="n"/>
+      <c r="C78" s="7" t="n"/>
     </row>
     <row r="79">
-      <c r="A79" s="3" t="n"/>
-      <c r="B79" s="3" t="n"/>
-      <c r="C79" s="3" t="n"/>
+      <c r="A79" s="6" t="n"/>
+      <c r="B79" s="7" t="n"/>
+      <c r="C79" s="7" t="n"/>
     </row>
     <row r="80">
-      <c r="A80" s="3" t="n"/>
-      <c r="B80" s="3" t="n"/>
-      <c r="C80" s="3" t="n"/>
+      <c r="A80" s="6" t="n"/>
+      <c r="B80" s="7" t="n"/>
+      <c r="C80" s="7" t="n"/>
     </row>
     <row r="81">
-      <c r="A81" s="3" t="n"/>
-      <c r="B81" s="3" t="n"/>
-      <c r="C81" s="3" t="n"/>
+      <c r="A81" s="6" t="n"/>
+      <c r="B81" s="7" t="n"/>
+      <c r="C81" s="7" t="n"/>
     </row>
     <row r="82">
-      <c r="A82" s="3" t="n"/>
-      <c r="B82" s="3" t="n"/>
-      <c r="C82" s="3" t="n"/>
+      <c r="A82" s="6" t="n"/>
+      <c r="B82" s="7" t="n"/>
+      <c r="C82" s="7" t="n"/>
     </row>
     <row r="83">
-      <c r="A83" s="3" t="n"/>
-      <c r="B83" s="3" t="n"/>
-      <c r="C83" s="3" t="n"/>
+      <c r="A83" s="6" t="n"/>
+      <c r="B83" s="7" t="n"/>
+      <c r="C83" s="7" t="n"/>
     </row>
     <row r="84">
-      <c r="A84" s="3" t="n"/>
-      <c r="B84" s="3" t="n"/>
-      <c r="C84" s="3" t="n"/>
+      <c r="A84" s="6" t="n"/>
+      <c r="B84" s="7" t="n"/>
+      <c r="C84" s="7" t="n"/>
     </row>
     <row r="85">
-      <c r="A85" s="3" t="n"/>
-      <c r="B85" s="3" t="n"/>
-      <c r="C85" s="3" t="n"/>
+      <c r="A85" s="6" t="n"/>
+      <c r="B85" s="7" t="n"/>
+      <c r="C85" s="7" t="n"/>
     </row>
     <row r="86">
-      <c r="A86" s="3" t="n"/>
-      <c r="B86" s="3" t="n"/>
-      <c r="C86" s="3" t="n"/>
+      <c r="A86" s="6" t="n"/>
+      <c r="B86" s="7" t="n"/>
+      <c r="C86" s="7" t="n"/>
     </row>
     <row r="87">
-      <c r="A87" s="3" t="n"/>
-      <c r="B87" s="3" t="n"/>
-      <c r="C87" s="3" t="n"/>
+      <c r="A87" s="6" t="n"/>
+      <c r="B87" s="7" t="n"/>
+      <c r="C87" s="7" t="n"/>
     </row>
     <row r="88">
-      <c r="A88" s="3" t="n"/>
-      <c r="B88" s="3" t="n"/>
-      <c r="C88" s="3" t="n"/>
+      <c r="A88" s="6" t="n"/>
+      <c r="B88" s="7" t="n"/>
+      <c r="C88" s="7" t="n"/>
     </row>
     <row r="89">
-      <c r="A89" s="3" t="n"/>
-      <c r="B89" s="3" t="n"/>
-      <c r="C89" s="3" t="n"/>
+      <c r="A89" s="6" t="n"/>
+      <c r="B89" s="7" t="n"/>
+      <c r="C89" s="7" t="n"/>
     </row>
     <row r="90">
-      <c r="A90" s="3" t="n"/>
-      <c r="B90" s="3" t="n"/>
-      <c r="C90" s="3" t="n"/>
+      <c r="A90" s="6" t="n"/>
+      <c r="B90" s="7" t="n"/>
+      <c r="C90" s="7" t="n"/>
     </row>
     <row r="91">
-      <c r="A91" s="3" t="n"/>
-      <c r="B91" s="3" t="n"/>
-      <c r="C91" s="3" t="n"/>
+      <c r="A91" s="6" t="n"/>
+      <c r="B91" s="7" t="n"/>
+      <c r="C91" s="7" t="n"/>
     </row>
     <row r="92">
-      <c r="A92" s="3" t="n"/>
-      <c r="B92" s="3" t="n"/>
-      <c r="C92" s="3" t="n"/>
+      <c r="A92" s="6" t="n"/>
+      <c r="B92" s="7" t="n"/>
+      <c r="C92" s="7" t="n"/>
     </row>
     <row r="93">
-      <c r="A93" s="3" t="n"/>
-      <c r="B93" s="3" t="n"/>
-      <c r="C93" s="3" t="n"/>
+      <c r="A93" s="6" t="n"/>
+      <c r="B93" s="7" t="n"/>
+      <c r="C93" s="7" t="n"/>
     </row>
     <row r="94">
-      <c r="A94" s="3" t="n"/>
-      <c r="B94" s="3" t="n"/>
-      <c r="C94" s="3" t="n"/>
+      <c r="A94" s="6" t="n"/>
+      <c r="B94" s="7" t="n"/>
+      <c r="C94" s="7" t="n"/>
     </row>
     <row r="95">
-      <c r="A95" s="3" t="n"/>
-      <c r="B95" s="3" t="n"/>
-      <c r="C95" s="3" t="n"/>
+      <c r="A95" s="6" t="n"/>
+      <c r="B95" s="7" t="n"/>
+      <c r="C95" s="7" t="n"/>
     </row>
     <row r="96">
-      <c r="A96" s="3" t="n"/>
-      <c r="B96" s="3" t="n"/>
-      <c r="C96" s="3" t="n"/>
+      <c r="A96" s="6" t="n"/>
+      <c r="B96" s="7" t="n"/>
+      <c r="C96" s="7" t="n"/>
     </row>
     <row r="97">
-      <c r="A97" s="3" t="n"/>
-      <c r="B97" s="3" t="n"/>
-      <c r="C97" s="3" t="n"/>
+      <c r="A97" s="6" t="n"/>
+      <c r="B97" s="7" t="n"/>
+      <c r="C97" s="7" t="n"/>
     </row>
     <row r="98">
-      <c r="A98" s="3" t="n"/>
-      <c r="B98" s="3" t="n"/>
-      <c r="C98" s="3" t="n"/>
+      <c r="A98" s="6" t="n"/>
+      <c r="B98" s="7" t="n"/>
+      <c r="C98" s="7" t="n"/>
     </row>
     <row r="99">
-      <c r="A99" s="3" t="n"/>
-      <c r="B99" s="3" t="n"/>
-      <c r="C99" s="3" t="n"/>
+      <c r="A99" s="6" t="n"/>
+      <c r="B99" s="7" t="n"/>
+      <c r="C99" s="7" t="n"/>
     </row>
     <row r="100">
-      <c r="A100" s="3" t="n"/>
-      <c r="B100" s="3" t="n"/>
-      <c r="C100" s="3" t="n"/>
+      <c r="A100" s="6" t="n"/>
+      <c r="B100" s="7" t="n"/>
+      <c r="C100" s="7" t="n"/>
     </row>
     <row r="101">
-      <c r="A101" s="3" t="n"/>
-      <c r="B101" s="3" t="n"/>
-      <c r="C101" s="3" t="n"/>
+      <c r="A101" s="6" t="n"/>
+      <c r="B101" s="7" t="n"/>
+      <c r="C101" s="7" t="n"/>
     </row>
     <row r="102">
-      <c r="A102" s="3" t="n"/>
-      <c r="B102" s="3" t="n"/>
-      <c r="C102" s="3" t="n"/>
+      <c r="A102" s="6" t="n"/>
+      <c r="B102" s="7" t="n"/>
+      <c r="C102" s="7" t="n"/>
     </row>
     <row r="103">
-      <c r="A103" s="3" t="n"/>
-      <c r="B103" s="3" t="n"/>
-      <c r="C103" s="3" t="n"/>
+      <c r="A103" s="6" t="n"/>
+      <c r="B103" s="7" t="n"/>
+      <c r="C103" s="7" t="n"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="6" t="n"/>
+      <c r="B104" s="7" t="n"/>
+      <c r="C104" s="7" t="n"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="6" t="n"/>
+      <c r="B105" s="7" t="n"/>
+      <c r="C105" s="7" t="n"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="6" t="n"/>
+      <c r="B106" s="7" t="n"/>
+      <c r="C106" s="7" t="n"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="6" t="n"/>
+      <c r="B107" s="7" t="n"/>
+      <c r="C107" s="7" t="n"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A4:A103">
-    <cfRule type="expression" priority="1" dxfId="0">
-      <formula>$A4="Open"</formula>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
+  <conditionalFormatting sqref="A8:A107">
+    <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="1">
+      <formula>$A8="Open"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A8:C107">
+    <cfRule type="expression" priority="2" dxfId="1">
+      <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="A4:A103" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="A8:A107" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Open,Answered,Later"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
--- a/tracker/templates/TEMPLATE_OpenQuestions.xlsx
+++ b/tracker/templates/TEMPLATE_OpenQuestions.xlsx
@@ -29,7 +29,7 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="001F4E78"/>
+      <color rgb="002B3C8E"/>
       <sz val="16"/>
     </font>
     <font>
@@ -49,22 +49,27 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00DDEBF7"/>
+        <fgColor rgb="00DCE0F0"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F4E78"/>
+        <fgColor rgb="002B3C8E"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
+    </border>
+    <border>
+      <bottom style="medium">
+        <color rgb="00FC7C36"/>
+      </bottom>
     </border>
     <border>
       <left style="thin">
@@ -80,23 +85,38 @@
         <color rgb="00BFBFBF"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="00FC7C36"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -494,553 +514,555 @@
           <t>OPEN QUESTIONS</t>
         </is>
       </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>Job number</t>
         </is>
       </c>
-      <c r="B2" s="3" t="n"/>
+      <c r="B2" s="4" t="n"/>
     </row>
     <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>Project name</t>
         </is>
       </c>
-      <c r="B3" s="3" t="n"/>
+      <c r="B3" s="4" t="n"/>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>Airco PM</t>
         </is>
       </c>
-      <c r="B4" s="3" t="n"/>
+      <c r="B4" s="4" t="n"/>
     </row>
     <row r="5">
-      <c r="B5" s="4">
+      <c r="B5" s="5">
         <f>COUNTIF(A8:A107,"Open")&amp;" open - ready to send when this is 0 and every unit and filter is accounted for"</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="34" customHeight="1">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" s="6" t="inlineStr">
         <is>
           <t>Question</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="6" t="inlineStr">
         <is>
           <t>Who knows</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="n"/>
-      <c r="B8" s="7" t="n"/>
-      <c r="C8" s="7" t="n"/>
+      <c r="A8" s="7" t="n"/>
+      <c r="B8" s="8" t="n"/>
+      <c r="C8" s="8" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="n"/>
-      <c r="B9" s="7" t="n"/>
-      <c r="C9" s="7" t="n"/>
+      <c r="A9" s="7" t="n"/>
+      <c r="B9" s="8" t="n"/>
+      <c r="C9" s="8" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="n"/>
-      <c r="B10" s="7" t="n"/>
-      <c r="C10" s="7" t="n"/>
+      <c r="A10" s="7" t="n"/>
+      <c r="B10" s="8" t="n"/>
+      <c r="C10" s="8" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="6" t="n"/>
-      <c r="B11" s="7" t="n"/>
-      <c r="C11" s="7" t="n"/>
+      <c r="A11" s="7" t="n"/>
+      <c r="B11" s="8" t="n"/>
+      <c r="C11" s="8" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="n"/>
-      <c r="B12" s="7" t="n"/>
-      <c r="C12" s="7" t="n"/>
+      <c r="A12" s="7" t="n"/>
+      <c r="B12" s="8" t="n"/>
+      <c r="C12" s="8" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="6" t="n"/>
-      <c r="B13" s="7" t="n"/>
-      <c r="C13" s="7" t="n"/>
+      <c r="A13" s="7" t="n"/>
+      <c r="B13" s="8" t="n"/>
+      <c r="C13" s="8" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="6" t="n"/>
-      <c r="B14" s="7" t="n"/>
-      <c r="C14" s="7" t="n"/>
+      <c r="A14" s="7" t="n"/>
+      <c r="B14" s="8" t="n"/>
+      <c r="C14" s="8" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="6" t="n"/>
-      <c r="B15" s="7" t="n"/>
-      <c r="C15" s="7" t="n"/>
+      <c r="A15" s="7" t="n"/>
+      <c r="B15" s="8" t="n"/>
+      <c r="C15" s="8" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="6" t="n"/>
-      <c r="B16" s="7" t="n"/>
-      <c r="C16" s="7" t="n"/>
+      <c r="A16" s="7" t="n"/>
+      <c r="B16" s="8" t="n"/>
+      <c r="C16" s="8" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="6" t="n"/>
-      <c r="B17" s="7" t="n"/>
-      <c r="C17" s="7" t="n"/>
+      <c r="A17" s="7" t="n"/>
+      <c r="B17" s="8" t="n"/>
+      <c r="C17" s="8" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="6" t="n"/>
-      <c r="B18" s="7" t="n"/>
-      <c r="C18" s="7" t="n"/>
+      <c r="A18" s="7" t="n"/>
+      <c r="B18" s="8" t="n"/>
+      <c r="C18" s="8" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="6" t="n"/>
-      <c r="B19" s="7" t="n"/>
-      <c r="C19" s="7" t="n"/>
+      <c r="A19" s="7" t="n"/>
+      <c r="B19" s="8" t="n"/>
+      <c r="C19" s="8" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="6" t="n"/>
-      <c r="B20" s="7" t="n"/>
-      <c r="C20" s="7" t="n"/>
+      <c r="A20" s="7" t="n"/>
+      <c r="B20" s="8" t="n"/>
+      <c r="C20" s="8" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="6" t="n"/>
-      <c r="B21" s="7" t="n"/>
-      <c r="C21" s="7" t="n"/>
+      <c r="A21" s="7" t="n"/>
+      <c r="B21" s="8" t="n"/>
+      <c r="C21" s="8" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="6" t="n"/>
-      <c r="B22" s="7" t="n"/>
-      <c r="C22" s="7" t="n"/>
+      <c r="A22" s="7" t="n"/>
+      <c r="B22" s="8" t="n"/>
+      <c r="C22" s="8" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="6" t="n"/>
-      <c r="B23" s="7" t="n"/>
-      <c r="C23" s="7" t="n"/>
+      <c r="A23" s="7" t="n"/>
+      <c r="B23" s="8" t="n"/>
+      <c r="C23" s="8" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="6" t="n"/>
-      <c r="B24" s="7" t="n"/>
-      <c r="C24" s="7" t="n"/>
+      <c r="A24" s="7" t="n"/>
+      <c r="B24" s="8" t="n"/>
+      <c r="C24" s="8" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="6" t="n"/>
-      <c r="B25" s="7" t="n"/>
-      <c r="C25" s="7" t="n"/>
+      <c r="A25" s="7" t="n"/>
+      <c r="B25" s="8" t="n"/>
+      <c r="C25" s="8" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="6" t="n"/>
-      <c r="B26" s="7" t="n"/>
-      <c r="C26" s="7" t="n"/>
+      <c r="A26" s="7" t="n"/>
+      <c r="B26" s="8" t="n"/>
+      <c r="C26" s="8" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="6" t="n"/>
-      <c r="B27" s="7" t="n"/>
-      <c r="C27" s="7" t="n"/>
+      <c r="A27" s="7" t="n"/>
+      <c r="B27" s="8" t="n"/>
+      <c r="C27" s="8" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="6" t="n"/>
-      <c r="B28" s="7" t="n"/>
-      <c r="C28" s="7" t="n"/>
+      <c r="A28" s="7" t="n"/>
+      <c r="B28" s="8" t="n"/>
+      <c r="C28" s="8" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="6" t="n"/>
-      <c r="B29" s="7" t="n"/>
-      <c r="C29" s="7" t="n"/>
+      <c r="A29" s="7" t="n"/>
+      <c r="B29" s="8" t="n"/>
+      <c r="C29" s="8" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="6" t="n"/>
-      <c r="B30" s="7" t="n"/>
-      <c r="C30" s="7" t="n"/>
+      <c r="A30" s="7" t="n"/>
+      <c r="B30" s="8" t="n"/>
+      <c r="C30" s="8" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="6" t="n"/>
-      <c r="B31" s="7" t="n"/>
-      <c r="C31" s="7" t="n"/>
+      <c r="A31" s="7" t="n"/>
+      <c r="B31" s="8" t="n"/>
+      <c r="C31" s="8" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="6" t="n"/>
-      <c r="B32" s="7" t="n"/>
-      <c r="C32" s="7" t="n"/>
+      <c r="A32" s="7" t="n"/>
+      <c r="B32" s="8" t="n"/>
+      <c r="C32" s="8" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="6" t="n"/>
-      <c r="B33" s="7" t="n"/>
-      <c r="C33" s="7" t="n"/>
+      <c r="A33" s="7" t="n"/>
+      <c r="B33" s="8" t="n"/>
+      <c r="C33" s="8" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="6" t="n"/>
-      <c r="B34" s="7" t="n"/>
-      <c r="C34" s="7" t="n"/>
+      <c r="A34" s="7" t="n"/>
+      <c r="B34" s="8" t="n"/>
+      <c r="C34" s="8" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="6" t="n"/>
-      <c r="B35" s="7" t="n"/>
-      <c r="C35" s="7" t="n"/>
+      <c r="A35" s="7" t="n"/>
+      <c r="B35" s="8" t="n"/>
+      <c r="C35" s="8" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="6" t="n"/>
-      <c r="B36" s="7" t="n"/>
-      <c r="C36" s="7" t="n"/>
+      <c r="A36" s="7" t="n"/>
+      <c r="B36" s="8" t="n"/>
+      <c r="C36" s="8" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="6" t="n"/>
-      <c r="B37" s="7" t="n"/>
-      <c r="C37" s="7" t="n"/>
+      <c r="A37" s="7" t="n"/>
+      <c r="B37" s="8" t="n"/>
+      <c r="C37" s="8" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="6" t="n"/>
-      <c r="B38" s="7" t="n"/>
-      <c r="C38" s="7" t="n"/>
+      <c r="A38" s="7" t="n"/>
+      <c r="B38" s="8" t="n"/>
+      <c r="C38" s="8" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="6" t="n"/>
-      <c r="B39" s="7" t="n"/>
-      <c r="C39" s="7" t="n"/>
+      <c r="A39" s="7" t="n"/>
+      <c r="B39" s="8" t="n"/>
+      <c r="C39" s="8" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="6" t="n"/>
-      <c r="B40" s="7" t="n"/>
-      <c r="C40" s="7" t="n"/>
+      <c r="A40" s="7" t="n"/>
+      <c r="B40" s="8" t="n"/>
+      <c r="C40" s="8" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="6" t="n"/>
-      <c r="B41" s="7" t="n"/>
-      <c r="C41" s="7" t="n"/>
+      <c r="A41" s="7" t="n"/>
+      <c r="B41" s="8" t="n"/>
+      <c r="C41" s="8" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="6" t="n"/>
-      <c r="B42" s="7" t="n"/>
-      <c r="C42" s="7" t="n"/>
+      <c r="A42" s="7" t="n"/>
+      <c r="B42" s="8" t="n"/>
+      <c r="C42" s="8" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="6" t="n"/>
-      <c r="B43" s="7" t="n"/>
-      <c r="C43" s="7" t="n"/>
+      <c r="A43" s="7" t="n"/>
+      <c r="B43" s="8" t="n"/>
+      <c r="C43" s="8" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="6" t="n"/>
-      <c r="B44" s="7" t="n"/>
-      <c r="C44" s="7" t="n"/>
+      <c r="A44" s="7" t="n"/>
+      <c r="B44" s="8" t="n"/>
+      <c r="C44" s="8" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="6" t="n"/>
-      <c r="B45" s="7" t="n"/>
-      <c r="C45" s="7" t="n"/>
+      <c r="A45" s="7" t="n"/>
+      <c r="B45" s="8" t="n"/>
+      <c r="C45" s="8" t="n"/>
     </row>
     <row r="46">
-      <c r="A46" s="6" t="n"/>
-      <c r="B46" s="7" t="n"/>
-      <c r="C46" s="7" t="n"/>
+      <c r="A46" s="7" t="n"/>
+      <c r="B46" s="8" t="n"/>
+      <c r="C46" s="8" t="n"/>
     </row>
     <row r="47">
-      <c r="A47" s="6" t="n"/>
-      <c r="B47" s="7" t="n"/>
-      <c r="C47" s="7" t="n"/>
+      <c r="A47" s="7" t="n"/>
+      <c r="B47" s="8" t="n"/>
+      <c r="C47" s="8" t="n"/>
     </row>
     <row r="48">
-      <c r="A48" s="6" t="n"/>
-      <c r="B48" s="7" t="n"/>
-      <c r="C48" s="7" t="n"/>
+      <c r="A48" s="7" t="n"/>
+      <c r="B48" s="8" t="n"/>
+      <c r="C48" s="8" t="n"/>
     </row>
     <row r="49">
-      <c r="A49" s="6" t="n"/>
-      <c r="B49" s="7" t="n"/>
-      <c r="C49" s="7" t="n"/>
+      <c r="A49" s="7" t="n"/>
+      <c r="B49" s="8" t="n"/>
+      <c r="C49" s="8" t="n"/>
     </row>
     <row r="50">
-      <c r="A50" s="6" t="n"/>
-      <c r="B50" s="7" t="n"/>
-      <c r="C50" s="7" t="n"/>
+      <c r="A50" s="7" t="n"/>
+      <c r="B50" s="8" t="n"/>
+      <c r="C50" s="8" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="6" t="n"/>
-      <c r="B51" s="7" t="n"/>
-      <c r="C51" s="7" t="n"/>
+      <c r="A51" s="7" t="n"/>
+      <c r="B51" s="8" t="n"/>
+      <c r="C51" s="8" t="n"/>
     </row>
     <row r="52">
-      <c r="A52" s="6" t="n"/>
-      <c r="B52" s="7" t="n"/>
-      <c r="C52" s="7" t="n"/>
+      <c r="A52" s="7" t="n"/>
+      <c r="B52" s="8" t="n"/>
+      <c r="C52" s="8" t="n"/>
     </row>
     <row r="53">
-      <c r="A53" s="6" t="n"/>
-      <c r="B53" s="7" t="n"/>
-      <c r="C53" s="7" t="n"/>
+      <c r="A53" s="7" t="n"/>
+      <c r="B53" s="8" t="n"/>
+      <c r="C53" s="8" t="n"/>
     </row>
     <row r="54">
-      <c r="A54" s="6" t="n"/>
-      <c r="B54" s="7" t="n"/>
-      <c r="C54" s="7" t="n"/>
+      <c r="A54" s="7" t="n"/>
+      <c r="B54" s="8" t="n"/>
+      <c r="C54" s="8" t="n"/>
     </row>
     <row r="55">
-      <c r="A55" s="6" t="n"/>
-      <c r="B55" s="7" t="n"/>
-      <c r="C55" s="7" t="n"/>
+      <c r="A55" s="7" t="n"/>
+      <c r="B55" s="8" t="n"/>
+      <c r="C55" s="8" t="n"/>
     </row>
     <row r="56">
-      <c r="A56" s="6" t="n"/>
-      <c r="B56" s="7" t="n"/>
-      <c r="C56" s="7" t="n"/>
+      <c r="A56" s="7" t="n"/>
+      <c r="B56" s="8" t="n"/>
+      <c r="C56" s="8" t="n"/>
     </row>
     <row r="57">
-      <c r="A57" s="6" t="n"/>
-      <c r="B57" s="7" t="n"/>
-      <c r="C57" s="7" t="n"/>
+      <c r="A57" s="7" t="n"/>
+      <c r="B57" s="8" t="n"/>
+      <c r="C57" s="8" t="n"/>
     </row>
     <row r="58">
-      <c r="A58" s="6" t="n"/>
-      <c r="B58" s="7" t="n"/>
-      <c r="C58" s="7" t="n"/>
+      <c r="A58" s="7" t="n"/>
+      <c r="B58" s="8" t="n"/>
+      <c r="C58" s="8" t="n"/>
     </row>
     <row r="59">
-      <c r="A59" s="6" t="n"/>
-      <c r="B59" s="7" t="n"/>
-      <c r="C59" s="7" t="n"/>
+      <c r="A59" s="7" t="n"/>
+      <c r="B59" s="8" t="n"/>
+      <c r="C59" s="8" t="n"/>
     </row>
     <row r="60">
-      <c r="A60" s="6" t="n"/>
-      <c r="B60" s="7" t="n"/>
-      <c r="C60" s="7" t="n"/>
+      <c r="A60" s="7" t="n"/>
+      <c r="B60" s="8" t="n"/>
+      <c r="C60" s="8" t="n"/>
     </row>
     <row r="61">
-      <c r="A61" s="6" t="n"/>
-      <c r="B61" s="7" t="n"/>
-      <c r="C61" s="7" t="n"/>
+      <c r="A61" s="7" t="n"/>
+      <c r="B61" s="8" t="n"/>
+      <c r="C61" s="8" t="n"/>
     </row>
     <row r="62">
-      <c r="A62" s="6" t="n"/>
-      <c r="B62" s="7" t="n"/>
-      <c r="C62" s="7" t="n"/>
+      <c r="A62" s="7" t="n"/>
+      <c r="B62" s="8" t="n"/>
+      <c r="C62" s="8" t="n"/>
     </row>
     <row r="63">
-      <c r="A63" s="6" t="n"/>
-      <c r="B63" s="7" t="n"/>
-      <c r="C63" s="7" t="n"/>
+      <c r="A63" s="7" t="n"/>
+      <c r="B63" s="8" t="n"/>
+      <c r="C63" s="8" t="n"/>
     </row>
     <row r="64">
-      <c r="A64" s="6" t="n"/>
-      <c r="B64" s="7" t="n"/>
-      <c r="C64" s="7" t="n"/>
+      <c r="A64" s="7" t="n"/>
+      <c r="B64" s="8" t="n"/>
+      <c r="C64" s="8" t="n"/>
     </row>
     <row r="65">
-      <c r="A65" s="6" t="n"/>
-      <c r="B65" s="7" t="n"/>
-      <c r="C65" s="7" t="n"/>
+      <c r="A65" s="7" t="n"/>
+      <c r="B65" s="8" t="n"/>
+      <c r="C65" s="8" t="n"/>
     </row>
     <row r="66">
-      <c r="A66" s="6" t="n"/>
-      <c r="B66" s="7" t="n"/>
-      <c r="C66" s="7" t="n"/>
+      <c r="A66" s="7" t="n"/>
+      <c r="B66" s="8" t="n"/>
+      <c r="C66" s="8" t="n"/>
     </row>
     <row r="67">
-      <c r="A67" s="6" t="n"/>
-      <c r="B67" s="7" t="n"/>
-      <c r="C67" s="7" t="n"/>
+      <c r="A67" s="7" t="n"/>
+      <c r="B67" s="8" t="n"/>
+      <c r="C67" s="8" t="n"/>
     </row>
     <row r="68">
-      <c r="A68" s="6" t="n"/>
-      <c r="B68" s="7" t="n"/>
-      <c r="C68" s="7" t="n"/>
+      <c r="A68" s="7" t="n"/>
+      <c r="B68" s="8" t="n"/>
+      <c r="C68" s="8" t="n"/>
     </row>
     <row r="69">
-      <c r="A69" s="6" t="n"/>
-      <c r="B69" s="7" t="n"/>
-      <c r="C69" s="7" t="n"/>
+      <c r="A69" s="7" t="n"/>
+      <c r="B69" s="8" t="n"/>
+      <c r="C69" s="8" t="n"/>
     </row>
     <row r="70">
-      <c r="A70" s="6" t="n"/>
-      <c r="B70" s="7" t="n"/>
-      <c r="C70" s="7" t="n"/>
+      <c r="A70" s="7" t="n"/>
+      <c r="B70" s="8" t="n"/>
+      <c r="C70" s="8" t="n"/>
     </row>
     <row r="71">
-      <c r="A71" s="6" t="n"/>
-      <c r="B71" s="7" t="n"/>
-      <c r="C71" s="7" t="n"/>
+      <c r="A71" s="7" t="n"/>
+      <c r="B71" s="8" t="n"/>
+      <c r="C71" s="8" t="n"/>
     </row>
     <row r="72">
-      <c r="A72" s="6" t="n"/>
-      <c r="B72" s="7" t="n"/>
-      <c r="C72" s="7" t="n"/>
+      <c r="A72" s="7" t="n"/>
+      <c r="B72" s="8" t="n"/>
+      <c r="C72" s="8" t="n"/>
     </row>
     <row r="73">
-      <c r="A73" s="6" t="n"/>
-      <c r="B73" s="7" t="n"/>
-      <c r="C73" s="7" t="n"/>
+      <c r="A73" s="7" t="n"/>
+      <c r="B73" s="8" t="n"/>
+      <c r="C73" s="8" t="n"/>
     </row>
     <row r="74">
-      <c r="A74" s="6" t="n"/>
-      <c r="B74" s="7" t="n"/>
-      <c r="C74" s="7" t="n"/>
+      <c r="A74" s="7" t="n"/>
+      <c r="B74" s="8" t="n"/>
+      <c r="C74" s="8" t="n"/>
     </row>
     <row r="75">
-      <c r="A75" s="6" t="n"/>
-      <c r="B75" s="7" t="n"/>
-      <c r="C75" s="7" t="n"/>
+      <c r="A75" s="7" t="n"/>
+      <c r="B75" s="8" t="n"/>
+      <c r="C75" s="8" t="n"/>
     </row>
     <row r="76">
-      <c r="A76" s="6" t="n"/>
-      <c r="B76" s="7" t="n"/>
-      <c r="C76" s="7" t="n"/>
+      <c r="A76" s="7" t="n"/>
+      <c r="B76" s="8" t="n"/>
+      <c r="C76" s="8" t="n"/>
     </row>
     <row r="77">
-      <c r="A77" s="6" t="n"/>
-      <c r="B77" s="7" t="n"/>
-      <c r="C77" s="7" t="n"/>
+      <c r="A77" s="7" t="n"/>
+      <c r="B77" s="8" t="n"/>
+      <c r="C77" s="8" t="n"/>
     </row>
     <row r="78">
-      <c r="A78" s="6" t="n"/>
-      <c r="B78" s="7" t="n"/>
-      <c r="C78" s="7" t="n"/>
+      <c r="A78" s="7" t="n"/>
+      <c r="B78" s="8" t="n"/>
+      <c r="C78" s="8" t="n"/>
     </row>
     <row r="79">
-      <c r="A79" s="6" t="n"/>
-      <c r="B79" s="7" t="n"/>
-      <c r="C79" s="7" t="n"/>
+      <c r="A79" s="7" t="n"/>
+      <c r="B79" s="8" t="n"/>
+      <c r="C79" s="8" t="n"/>
     </row>
     <row r="80">
-      <c r="A80" s="6" t="n"/>
-      <c r="B80" s="7" t="n"/>
-      <c r="C80" s="7" t="n"/>
+      <c r="A80" s="7" t="n"/>
+      <c r="B80" s="8" t="n"/>
+      <c r="C80" s="8" t="n"/>
     </row>
     <row r="81">
-      <c r="A81" s="6" t="n"/>
-      <c r="B81" s="7" t="n"/>
-      <c r="C81" s="7" t="n"/>
+      <c r="A81" s="7" t="n"/>
+      <c r="B81" s="8" t="n"/>
+      <c r="C81" s="8" t="n"/>
     </row>
     <row r="82">
-      <c r="A82" s="6" t="n"/>
-      <c r="B82" s="7" t="n"/>
-      <c r="C82" s="7" t="n"/>
+      <c r="A82" s="7" t="n"/>
+      <c r="B82" s="8" t="n"/>
+      <c r="C82" s="8" t="n"/>
     </row>
     <row r="83">
-      <c r="A83" s="6" t="n"/>
-      <c r="B83" s="7" t="n"/>
-      <c r="C83" s="7" t="n"/>
+      <c r="A83" s="7" t="n"/>
+      <c r="B83" s="8" t="n"/>
+      <c r="C83" s="8" t="n"/>
     </row>
     <row r="84">
-      <c r="A84" s="6" t="n"/>
-      <c r="B84" s="7" t="n"/>
-      <c r="C84" s="7" t="n"/>
+      <c r="A84" s="7" t="n"/>
+      <c r="B84" s="8" t="n"/>
+      <c r="C84" s="8" t="n"/>
     </row>
     <row r="85">
-      <c r="A85" s="6" t="n"/>
-      <c r="B85" s="7" t="n"/>
-      <c r="C85" s="7" t="n"/>
+      <c r="A85" s="7" t="n"/>
+      <c r="B85" s="8" t="n"/>
+      <c r="C85" s="8" t="n"/>
     </row>
     <row r="86">
-      <c r="A86" s="6" t="n"/>
-      <c r="B86" s="7" t="n"/>
-      <c r="C86" s="7" t="n"/>
+      <c r="A86" s="7" t="n"/>
+      <c r="B86" s="8" t="n"/>
+      <c r="C86" s="8" t="n"/>
     </row>
     <row r="87">
-      <c r="A87" s="6" t="n"/>
-      <c r="B87" s="7" t="n"/>
-      <c r="C87" s="7" t="n"/>
+      <c r="A87" s="7" t="n"/>
+      <c r="B87" s="8" t="n"/>
+      <c r="C87" s="8" t="n"/>
     </row>
     <row r="88">
-      <c r="A88" s="6" t="n"/>
-      <c r="B88" s="7" t="n"/>
-      <c r="C88" s="7" t="n"/>
+      <c r="A88" s="7" t="n"/>
+      <c r="B88" s="8" t="n"/>
+      <c r="C88" s="8" t="n"/>
     </row>
     <row r="89">
-      <c r="A89" s="6" t="n"/>
-      <c r="B89" s="7" t="n"/>
-      <c r="C89" s="7" t="n"/>
+      <c r="A89" s="7" t="n"/>
+      <c r="B89" s="8" t="n"/>
+      <c r="C89" s="8" t="n"/>
     </row>
     <row r="90">
-      <c r="A90" s="6" t="n"/>
-      <c r="B90" s="7" t="n"/>
-      <c r="C90" s="7" t="n"/>
+      <c r="A90" s="7" t="n"/>
+      <c r="B90" s="8" t="n"/>
+      <c r="C90" s="8" t="n"/>
     </row>
     <row r="91">
-      <c r="A91" s="6" t="n"/>
-      <c r="B91" s="7" t="n"/>
-      <c r="C91" s="7" t="n"/>
+      <c r="A91" s="7" t="n"/>
+      <c r="B91" s="8" t="n"/>
+      <c r="C91" s="8" t="n"/>
     </row>
     <row r="92">
-      <c r="A92" s="6" t="n"/>
-      <c r="B92" s="7" t="n"/>
-      <c r="C92" s="7" t="n"/>
+      <c r="A92" s="7" t="n"/>
+      <c r="B92" s="8" t="n"/>
+      <c r="C92" s="8" t="n"/>
     </row>
     <row r="93">
-      <c r="A93" s="6" t="n"/>
-      <c r="B93" s="7" t="n"/>
-      <c r="C93" s="7" t="n"/>
+      <c r="A93" s="7" t="n"/>
+      <c r="B93" s="8" t="n"/>
+      <c r="C93" s="8" t="n"/>
     </row>
     <row r="94">
-      <c r="A94" s="6" t="n"/>
-      <c r="B94" s="7" t="n"/>
-      <c r="C94" s="7" t="n"/>
+      <c r="A94" s="7" t="n"/>
+      <c r="B94" s="8" t="n"/>
+      <c r="C94" s="8" t="n"/>
     </row>
     <row r="95">
-      <c r="A95" s="6" t="n"/>
-      <c r="B95" s="7" t="n"/>
-      <c r="C95" s="7" t="n"/>
+      <c r="A95" s="7" t="n"/>
+      <c r="B95" s="8" t="n"/>
+      <c r="C95" s="8" t="n"/>
     </row>
     <row r="96">
-      <c r="A96" s="6" t="n"/>
-      <c r="B96" s="7" t="n"/>
-      <c r="C96" s="7" t="n"/>
+      <c r="A96" s="7" t="n"/>
+      <c r="B96" s="8" t="n"/>
+      <c r="C96" s="8" t="n"/>
     </row>
     <row r="97">
-      <c r="A97" s="6" t="n"/>
-      <c r="B97" s="7" t="n"/>
-      <c r="C97" s="7" t="n"/>
+      <c r="A97" s="7" t="n"/>
+      <c r="B97" s="8" t="n"/>
+      <c r="C97" s="8" t="n"/>
     </row>
     <row r="98">
-      <c r="A98" s="6" t="n"/>
-      <c r="B98" s="7" t="n"/>
-      <c r="C98" s="7" t="n"/>
+      <c r="A98" s="7" t="n"/>
+      <c r="B98" s="8" t="n"/>
+      <c r="C98" s="8" t="n"/>
     </row>
     <row r="99">
-      <c r="A99" s="6" t="n"/>
-      <c r="B99" s="7" t="n"/>
-      <c r="C99" s="7" t="n"/>
+      <c r="A99" s="7" t="n"/>
+      <c r="B99" s="8" t="n"/>
+      <c r="C99" s="8" t="n"/>
     </row>
     <row r="100">
-      <c r="A100" s="6" t="n"/>
-      <c r="B100" s="7" t="n"/>
-      <c r="C100" s="7" t="n"/>
+      <c r="A100" s="7" t="n"/>
+      <c r="B100" s="8" t="n"/>
+      <c r="C100" s="8" t="n"/>
     </row>
     <row r="101">
-      <c r="A101" s="6" t="n"/>
-      <c r="B101" s="7" t="n"/>
-      <c r="C101" s="7" t="n"/>
+      <c r="A101" s="7" t="n"/>
+      <c r="B101" s="8" t="n"/>
+      <c r="C101" s="8" t="n"/>
     </row>
     <row r="102">
-      <c r="A102" s="6" t="n"/>
-      <c r="B102" s="7" t="n"/>
-      <c r="C102" s="7" t="n"/>
+      <c r="A102" s="7" t="n"/>
+      <c r="B102" s="8" t="n"/>
+      <c r="C102" s="8" t="n"/>
     </row>
     <row r="103">
-      <c r="A103" s="6" t="n"/>
-      <c r="B103" s="7" t="n"/>
-      <c r="C103" s="7" t="n"/>
+      <c r="A103" s="7" t="n"/>
+      <c r="B103" s="8" t="n"/>
+      <c r="C103" s="8" t="n"/>
     </row>
     <row r="104">
-      <c r="A104" s="6" t="n"/>
-      <c r="B104" s="7" t="n"/>
-      <c r="C104" s="7" t="n"/>
+      <c r="A104" s="7" t="n"/>
+      <c r="B104" s="8" t="n"/>
+      <c r="C104" s="8" t="n"/>
     </row>
     <row r="105">
-      <c r="A105" s="6" t="n"/>
-      <c r="B105" s="7" t="n"/>
-      <c r="C105" s="7" t="n"/>
+      <c r="A105" s="7" t="n"/>
+      <c r="B105" s="8" t="n"/>
+      <c r="C105" s="8" t="n"/>
     </row>
     <row r="106">
-      <c r="A106" s="6" t="n"/>
-      <c r="B106" s="7" t="n"/>
-      <c r="C106" s="7" t="n"/>
+      <c r="A106" s="7" t="n"/>
+      <c r="B106" s="8" t="n"/>
+      <c r="C106" s="8" t="n"/>
     </row>
     <row r="107">
-      <c r="A107" s="6" t="n"/>
-      <c r="B107" s="7" t="n"/>
-      <c r="C107" s="7" t="n"/>
+      <c r="A107" s="7" t="n"/>
+      <c r="B107" s="8" t="n"/>
+      <c r="C107" s="8" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/tracker/templates/TEMPLATE_OpenQuestions.xlsx
+++ b/tracker/templates/TEMPLATE_OpenQuestions.xlsx
@@ -117,7 +117,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
